--- a/docs/unit1/4_graphing_numsolver/(Starter-Workbook)-Class-Graphing-and-Solver.xlsx
+++ b/docs/unit1/4_graphing_numsolver/(Starter-Workbook)-Class-Graphing-and-Solver.xlsx
@@ -735,7 +735,7 @@
   <x:autoFilter ref="A1:M1001"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Date" dataDxfId="12"/>
-    <x:tableColumn id="2" name="Month" dataDxfId="11"/>
+    <x:tableColumn id="2" name="Month Start" dataDxfId="11"/>
     <x:tableColumn id="3" name="Region" dataDxfId="10"/>
     <x:tableColumn id="4" name="Product" dataDxfId="9"/>
     <x:tableColumn id="5" name="Units Sold" dataDxfId="8"/>
